--- a/data/raw/prum.xlsx
+++ b/data/raw/prum.xlsx
@@ -1084,7 +1084,7 @@
     <t xml:space="preserve">Zdroj: Český statistický úřad</t>
   </si>
   <si>
-    <t xml:space="preserve">Časová řada generována: 29.05.2023 17:52:32</t>
+    <t xml:space="preserve">Časová řada generována: 30.05.2023 11:26:10</t>
   </si>
 </sst>
 </file>
